--- a/web/public/forms/anjeon-gyehoek.xlsx
+++ b/web/public/forms/anjeon-gyehoek.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전관리계획서 표지·목차" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'안전관리계획서 표지·목차'!$A$1:$X$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0;;&quot;&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,32 +37,53 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +92,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +116,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +141,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,15 +583,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +615,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +645,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +675,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +705,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -682,7 +735,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -712,7 +765,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -733,13 +786,13 @@
     </row>
     <row r="11" ht="6" customHeight="1"/>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>목    차</t>
         </is>
@@ -761,7 +814,7 @@
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
       <c r="T12" s="5" t="n"/>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>쪽</t>
         </is>
@@ -771,9 +824,16 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr"/>
+      <c r="A13" s="9">
+        <f>IF(C13="","",COUNTA(C13:C13))</f>
+        <v/>
+      </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>공사개요</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
@@ -791,15 +851,22 @@
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
       <c r="T13" s="5" t="n"/>
-      <c r="U13" s="8" t="inlineStr"/>
+      <c r="U13" s="11" t="n"/>
       <c r="V13" s="5" t="n"/>
       <c r="W13" s="5" t="n"/>
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr"/>
+      <c r="A14" s="9">
+        <f>IF(C14="","",COUNTA(C13:C14))</f>
+        <v/>
+      </c>
       <c r="B14" s="5" t="n"/>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>현장 특성과 위험요인</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
@@ -817,15 +884,22 @@
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
       <c r="T14" s="5" t="n"/>
-      <c r="U14" s="8" t="inlineStr"/>
+      <c r="U14" s="11" t="n"/>
       <c r="V14" s="5" t="n"/>
       <c r="W14" s="5" t="n"/>
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr"/>
+      <c r="A15" s="9">
+        <f>IF(C15="","",COUNTA(C13:C15))</f>
+        <v/>
+      </c>
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>안전관리조직</t>
+        </is>
+      </c>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
@@ -843,15 +917,22 @@
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
       <c r="T15" s="5" t="n"/>
-      <c r="U15" s="8" t="inlineStr"/>
+      <c r="U15" s="11" t="n"/>
       <c r="V15" s="5" t="n"/>
       <c r="W15" s="5" t="n"/>
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr"/>
+      <c r="A16" s="9">
+        <f>IF(C16="","",COUNTA(C13:C16))</f>
+        <v/>
+      </c>
       <c r="B16" s="5" t="n"/>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>공종별 안전관리계획</t>
+        </is>
+      </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
@@ -869,15 +950,22 @@
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
       <c r="T16" s="5" t="n"/>
-      <c r="U16" s="8" t="inlineStr"/>
+      <c r="U16" s="11" t="n"/>
       <c r="V16" s="5" t="n"/>
       <c r="W16" s="5" t="n"/>
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr"/>
+      <c r="A17" s="9">
+        <f>IF(C17="","",COUNTA(C13:C17))</f>
+        <v/>
+      </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>가설구조물 검토</t>
+        </is>
+      </c>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
@@ -895,15 +983,22 @@
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
-      <c r="U17" s="8" t="inlineStr"/>
+      <c r="U17" s="11" t="n"/>
       <c r="V17" s="5" t="n"/>
       <c r="W17" s="5" t="n"/>
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr"/>
+      <c r="A18" s="9">
+        <f>IF(C18="","",COUNTA(C13:C18))</f>
+        <v/>
+      </c>
       <c r="B18" s="5" t="n"/>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>안전점검계획</t>
+        </is>
+      </c>
       <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
@@ -921,15 +1016,22 @@
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
-      <c r="U18" s="8" t="inlineStr"/>
+      <c r="U18" s="11" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr"/>
+      <c r="A19" s="9">
+        <f>IF(C19="","",COUNTA(C13:C19))</f>
+        <v/>
+      </c>
       <c r="B19" s="5" t="n"/>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>안전교육계획</t>
+        </is>
+      </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
@@ -947,15 +1049,22 @@
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
-      <c r="U19" s="8" t="inlineStr"/>
+      <c r="U19" s="11" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr"/>
+      <c r="A20" s="9">
+        <f>IF(C20="","",COUNTA(C13:C20))</f>
+        <v/>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>비상시 조치계획</t>
+        </is>
+      </c>
       <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
@@ -973,15 +1082,22 @@
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
-      <c r="U20" s="8" t="inlineStr"/>
+      <c r="U20" s="11" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr"/>
+      <c r="A21" s="9">
+        <f>IF(C21="","",COUNTA(C13:C21))</f>
+        <v/>
+      </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>안전관리비 집행계획</t>
+        </is>
+      </c>
       <c r="D21" s="5" t="n"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
@@ -999,15 +1115,18 @@
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
-      <c r="U21" s="8" t="inlineStr"/>
+      <c r="U21" s="11" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr"/>
+      <c r="A22" s="9">
+        <f>IF(C22="","",COUNTA(C13:C22))</f>
+        <v/>
+      </c>
       <c r="B22" s="5" t="n"/>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="10" t="n"/>
       <c r="D22" s="5" t="n"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
@@ -1025,15 +1144,18 @@
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
-      <c r="U22" s="8" t="inlineStr"/>
+      <c r="U22" s="11" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr"/>
+      <c r="A23" s="9">
+        <f>IF(C23="","",COUNTA(C13:C23))</f>
+        <v/>
+      </c>
       <c r="B23" s="5" t="n"/>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="10" t="n"/>
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
@@ -1051,15 +1173,18 @@
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
-      <c r="U23" s="8" t="inlineStr"/>
+      <c r="U23" s="11" t="n"/>
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr"/>
+      <c r="A24" s="9">
+        <f>IF(C24="","",COUNTA(C13:C24))</f>
+        <v/>
+      </c>
       <c r="B24" s="5" t="n"/>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="10" t="n"/>
       <c r="D24" s="5" t="n"/>
       <c r="E24" s="5" t="n"/>
       <c r="F24" s="5" t="n"/>
@@ -1077,14 +1202,14 @@
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
-      <c r="U24" s="8" t="inlineStr"/>
+      <c r="U24" s="11" t="n"/>
       <c r="V24" s="5" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+    <row r="26" ht="48.5" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>※ 목차 예: 1. 공사개요  2. 현장 특성과 위험요인  3. 안전관리조직  4. 공종별 안전관리계획  5. 가설구조물 검토  6. 안전점검계획  7. 안전교육계획  8. 비상시 조치계획  9. 안전관리비 집행계획</t>
         </is>
@@ -1093,54 +1218,66 @@
     <row r="27" ht="6" customHeight="1"/>
     <row r="28" ht="10" customHeight="1"/>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="K30" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="14" t="inlineStr"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="Q30" s="16" t="n"/>
+      <c r="U30" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="K31" s="11" t="inlineStr">
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="14" t="inlineStr"/>
+      <c r="K31" s="15" t="inlineStr">
         <is>
           <t>대표자</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="Q31" s="16" t="n"/>
+      <c r="U31" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="66">
     <mergeCell ref="C20:T20"/>
     <mergeCell ref="U18:X18"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="G7:X7"/>
-    <mergeCell ref="K30:R30"/>
+    <mergeCell ref="Q30:T30"/>
     <mergeCell ref="C16:T16"/>
     <mergeCell ref="G10:X10"/>
+    <mergeCell ref="K31:P31"/>
     <mergeCell ref="C22:T22"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="U20:X20"/>
@@ -1151,17 +1288,18 @@
     <mergeCell ref="U19:X19"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C21:T21"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A26:X26"/>
+    <mergeCell ref="U31:X31"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="U22:X22"/>
     <mergeCell ref="G5:X5"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A30:J30"/>
     <mergeCell ref="U15:X15"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="C17:T17"/>
     <mergeCell ref="C23:T23"/>
-    <mergeCell ref="S30:X30"/>
-    <mergeCell ref="K31:R31"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A10:F10"/>
@@ -1169,6 +1307,7 @@
     <mergeCell ref="A35:X35"/>
     <mergeCell ref="C19:T19"/>
     <mergeCell ref="A9:F9"/>
+    <mergeCell ref="U30:X30"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="C13:T13"/>
     <mergeCell ref="U17:X17"/>
@@ -1176,11 +1315,13 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="S31:X31"/>
     <mergeCell ref="U16:X16"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K30:P30"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A34:X34"/>
     <mergeCell ref="C15:T15"/>
+    <mergeCell ref="Q31:T31"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C24:T24"/>
     <mergeCell ref="A1:L1"/>
@@ -1195,7 +1336,841 @@
     <mergeCell ref="G8:X8"/>
     <mergeCell ref="U24:X24"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>안 전 관 리 계 획 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공사 규모</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>배수로 L=742m · 집수정 18곳 · 암거 85m</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공사 기간</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작성일자</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  안전관리책임자</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>김철수(현장대리인)</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작성자(자격)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>정안전(산업안전기사)</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="6" customHeight="1"/>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>목    차</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>쪽</t>
+        </is>
+      </c>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="9">
+        <f>IF(C13="","",COUNTA(C13:C13))</f>
+        <v/>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>공사개요</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="9">
+        <f>IF(C14="","",COUNTA(C13:C14))</f>
+        <v/>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>현장 특성과 위험요인</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="5" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="5" t="n"/>
+      <c r="U14" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" s="5" t="n"/>
+      <c r="W14" s="5" t="n"/>
+      <c r="X14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="9">
+        <f>IF(C15="","",COUNTA(C13:C15))</f>
+        <v/>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>안전관리조직</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="5" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="5" t="n"/>
+      <c r="U15" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="V15" s="5" t="n"/>
+      <c r="W15" s="5" t="n"/>
+      <c r="X15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="9">
+        <f>IF(C16="","",COUNTA(C13:C16))</f>
+        <v/>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>공종별 안전관리계획</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="5" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="5" t="n"/>
+      <c r="U16" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="V16" s="5" t="n"/>
+      <c r="W16" s="5" t="n"/>
+      <c r="X16" s="5" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9">
+        <f>IF(C17="","",COUNTA(C13:C17))</f>
+        <v/>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>가설구조물 검토</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9">
+        <f>IF(C18="","",COUNTA(C13:C18))</f>
+        <v/>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>안전점검계획</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9">
+        <f>IF(C19="","",COUNTA(C13:C19))</f>
+        <v/>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>안전교육계획</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9">
+        <f>IF(C20="","",COUNTA(C13:C20))</f>
+        <v/>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>비상시 조치계획</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9">
+        <f>IF(C21="","",COUNTA(C13:C21))</f>
+        <v/>
+      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>안전관리비 집행계획</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="11" t="n">
+        <v>78</v>
+      </c>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9">
+        <f>IF(C22="","",COUNTA(C13:C22))</f>
+        <v/>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="11" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9">
+        <f>IF(C23="","",COUNTA(C13:C23))</f>
+        <v/>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9">
+        <f>IF(C24="","",COUNTA(C13:C24))</f>
+        <v/>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="11" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="48.5" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>※ 목차 예: 1. 공사개요  2. 현장 특성과 위험요인  3. 안전관리조직  4. 공종별 안전관리계획  5. 가설구조물 검토  6. 안전점검계획  7. 안전교육계획  8. 비상시 조치계획  9. 안전관리비 집행계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="10" customHeight="1"/>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="14" t="inlineStr"/>
+      <c r="K30" s="15" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q30" s="16" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U30" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="14" t="inlineStr"/>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>대표자</t>
+        </is>
+      </c>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>홍길동</t>
+        </is>
+      </c>
+      <c r="U31" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="65">
+    <mergeCell ref="C20:T20"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="C16:T16"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="K31:P31"/>
+    <mergeCell ref="C22:T22"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="U14:X14"/>
+    <mergeCell ref="C12:T12"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C21:T21"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A26:X26"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="U15:X15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C17:T17"/>
+    <mergeCell ref="C23:T23"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="C19:T19"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C13:T13"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="C18:T18"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K30:P30"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A34:X34"/>
+    <mergeCell ref="C15:T15"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C24:T24"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="C14:T14"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="U12:X12"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="U24:X24"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/anjeon-gyehoek.xlsx
+++ b/web/public/forms/anjeon-gyehoek.xlsx
@@ -586,7 +586,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">

--- a/web/public/forms/anjeon-gyehoek.xlsx
+++ b/web/public/forms/anjeon-gyehoek.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안전관리계획서 표지·목차" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'안전관리계획서 표지·목차'!$A$1:$X$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -132,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -185,9 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -824,10 +819,7 @@
       <c r="X12" s="5" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9">
-        <f>IF(C13="","",COUNTA(C13:C13))</f>
-        <v/>
-      </c>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="10" t="inlineStr">
         <is>
@@ -857,10 +849,7 @@
       <c r="X13" s="5" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9">
-        <f>IF(C14="","",COUNTA(C13:C14))</f>
-        <v/>
-      </c>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="10" t="inlineStr">
         <is>
@@ -890,10 +879,7 @@
       <c r="X14" s="5" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9">
-        <f>IF(C15="","",COUNTA(C13:C15))</f>
-        <v/>
-      </c>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="10" t="inlineStr">
         <is>
@@ -923,10 +909,7 @@
       <c r="X15" s="5" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9">
-        <f>IF(C16="","",COUNTA(C13:C16))</f>
-        <v/>
-      </c>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="10" t="inlineStr">
         <is>
@@ -956,10 +939,7 @@
       <c r="X16" s="5" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9">
-        <f>IF(C17="","",COUNTA(C13:C17))</f>
-        <v/>
-      </c>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="10" t="inlineStr">
         <is>
@@ -989,10 +969,7 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9">
-        <f>IF(C18="","",COUNTA(C13:C18))</f>
-        <v/>
-      </c>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="10" t="inlineStr">
         <is>
@@ -1022,10 +999,7 @@
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9">
-        <f>IF(C19="","",COUNTA(C13:C19))</f>
-        <v/>
-      </c>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="10" t="inlineStr">
         <is>
@@ -1055,10 +1029,7 @@
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9">
-        <f>IF(C20="","",COUNTA(C13:C20))</f>
-        <v/>
-      </c>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="10" t="inlineStr">
         <is>
@@ -1088,10 +1059,7 @@
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9">
-        <f>IF(C21="","",COUNTA(C13:C21))</f>
-        <v/>
-      </c>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="10" t="inlineStr">
         <is>
@@ -1121,10 +1089,7 @@
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9">
-        <f>IF(C22="","",COUNTA(C13:C22))</f>
-        <v/>
-      </c>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="5" t="n"/>
@@ -1150,10 +1115,7 @@
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9">
-        <f>IF(C23="","",COUNTA(C13:C23))</f>
-        <v/>
-      </c>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="5" t="n"/>
@@ -1179,10 +1141,7 @@
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9">
-        <f>IF(C24="","",COUNTA(C13:C24))</f>
-        <v/>
-      </c>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="5" t="n"/>
@@ -1253,6 +1212,7 @@
       </c>
     </row>
     <row r="32" ht="6" customHeight="1"/>
+    <row r="33"/>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="18" t="inlineStr">
         <is>
@@ -1340,837 +1300,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>안 전 관 리 계 획 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공사 규모</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>배수로 L=742m · 집수정 18곳 · 암거 85m</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공사 기간</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작성일자</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="7" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  안전관리책임자</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>김철수(현장대리인)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작성자(자격)</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>정안전(산업안전기사)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="6" customHeight="1"/>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>목    차</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>쪽</t>
-        </is>
-      </c>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9">
-        <f>IF(C13="","",COUNTA(C13:C13))</f>
-        <v/>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>공사개요</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9">
-        <f>IF(C14="","",COUNTA(C13:C14))</f>
-        <v/>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>현장 특성과 위험요인</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="5" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="5" t="n"/>
-      <c r="L14" s="5" t="n"/>
-      <c r="M14" s="5" t="n"/>
-      <c r="N14" s="5" t="n"/>
-      <c r="O14" s="5" t="n"/>
-      <c r="P14" s="5" t="n"/>
-      <c r="Q14" s="5" t="n"/>
-      <c r="R14" s="5" t="n"/>
-      <c r="S14" s="5" t="n"/>
-      <c r="T14" s="5" t="n"/>
-      <c r="U14" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V14" s="5" t="n"/>
-      <c r="W14" s="5" t="n"/>
-      <c r="X14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="9">
-        <f>IF(C15="","",COUNTA(C13:C15))</f>
-        <v/>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>안전관리조직</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="5" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="5" t="n"/>
-      <c r="L15" s="5" t="n"/>
-      <c r="M15" s="5" t="n"/>
-      <c r="N15" s="5" t="n"/>
-      <c r="O15" s="5" t="n"/>
-      <c r="P15" s="5" t="n"/>
-      <c r="Q15" s="5" t="n"/>
-      <c r="R15" s="5" t="n"/>
-      <c r="S15" s="5" t="n"/>
-      <c r="T15" s="5" t="n"/>
-      <c r="U15" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="V15" s="5" t="n"/>
-      <c r="W15" s="5" t="n"/>
-      <c r="X15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="9">
-        <f>IF(C16="","",COUNTA(C13:C16))</f>
-        <v/>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>공종별 안전관리계획</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="5" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="5" t="n"/>
-      <c r="L16" s="5" t="n"/>
-      <c r="M16" s="5" t="n"/>
-      <c r="N16" s="5" t="n"/>
-      <c r="O16" s="5" t="n"/>
-      <c r="P16" s="5" t="n"/>
-      <c r="Q16" s="5" t="n"/>
-      <c r="R16" s="5" t="n"/>
-      <c r="S16" s="5" t="n"/>
-      <c r="T16" s="5" t="n"/>
-      <c r="U16" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="V16" s="5" t="n"/>
-      <c r="W16" s="5" t="n"/>
-      <c r="X16" s="5" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="9">
-        <f>IF(C17="","",COUNTA(C13:C17))</f>
-        <v/>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>가설구조물 검토</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="5" t="n"/>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="5" t="n"/>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9">
-        <f>IF(C18="","",COUNTA(C13:C18))</f>
-        <v/>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>안전점검계획</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="5" t="n"/>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="5" t="n"/>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9">
-        <f>IF(C19="","",COUNTA(C13:C19))</f>
-        <v/>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>안전교육계획</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="5" t="n"/>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="5" t="n"/>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9">
-        <f>IF(C20="","",COUNTA(C13:C20))</f>
-        <v/>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>비상시 조치계획</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="5" t="n"/>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="5" t="n"/>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9">
-        <f>IF(C21="","",COUNTA(C13:C21))</f>
-        <v/>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>안전관리비 집행계획</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="5" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="5" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9">
-        <f>IF(C22="","",COUNTA(C13:C22))</f>
-        <v/>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="5" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9">
-        <f>IF(C23="","",COUNTA(C13:C23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9">
-        <f>IF(C24="","",COUNTA(C13:C24))</f>
-        <v/>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="48.5" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>※ 목차 예: 1. 공사개요  2. 현장 특성과 위험요인  3. 안전관리조직  4. 공종별 안전관리계획  5. 가설구조물 검토  6. 안전점검계획  7. 안전교육계획  8. 비상시 조치계획  9. 안전관리비 집행계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="10" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="14" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q30" s="16" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U30" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="14" t="inlineStr"/>
-      <c r="K31" s="15" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="Q31" s="16" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="U31" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="65">
-    <mergeCell ref="C20:T20"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="C16:T16"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="K31:P31"/>
-    <mergeCell ref="C22:T22"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="U14:X14"/>
-    <mergeCell ref="C12:T12"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C21:T21"/>
-    <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A26:X26"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="U15:X15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C17:T17"/>
-    <mergeCell ref="C23:T23"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="C19:T19"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C13:T13"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="C18:T18"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K30:P30"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A34:X34"/>
-    <mergeCell ref="C15:T15"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C24:T24"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="C14:T14"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="U12:X12"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="U24:X24"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/anjeon-gyehoek.xlsx
+++ b/web/public/forms/anjeon-gyehoek.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
